--- a/data_extactor/batch_10_fa/batch_0055_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0055_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعالانه | تفکر انتقادی | سخن گفتن | درک مطلب خوانده‌شده | مانیتورینگ | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>قانون و حکومت | ایمنی و امنیت عمومی | زیست‌شناسی | زبان انگلیسی | خدمات مشتریان و پرسنلی | روان‌شناسی | جغرافیا | جامعه‌شناسی و انسان‌شناسی | آموزش و تربیت | مدیریت و سازماندهی | امور اداری | کامپیوتر و الکترونیک | ارتباطات و رسانه</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | زیست‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | جغرافیا | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | مدیریت و اداره | اداری | رایانه و الکترونیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال استقرایی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | بینایی دور | درک کتبی | بیان کتبی | انعطاف‌پذیری بستار | جهت‌یابی فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | سرعت بستار | ادراک عمق | استقامت بدنی | هماهنگی چند عضو | دقت کنترل | اشتراک زمانی | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال استقرایی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | بینایی دور | درک کتبی | بیان کتبی | انعطاف‌پذیری بستار | جهت‌گیری فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | سرعت بستار | درک عمق | استقامت | هماهنگی چند عضو | دقت کنترل | تقسیم توجه | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | مکالمات تلفنی | فضای باز، در معرض همه شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | ایمیل | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد اشتباه | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا منظم بودن | دفعات تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | فشار زمانی | در معرض دماهای بسیار گرم یا سرد | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سطح رقابت | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌زدگی‌ها | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | مکالمات تلفنی | فضای باز، در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | فشار زمانی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سطح رقابت | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارکنان کنترل حیوانات | زیست‌شناسان | دانشمندان حفاظت از محیط زیست | بازرسان انطباق محیطی | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست، از جمله بهداشت | سرپرستان رده اول کارگران کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان رده اول کارگران آتش‌نشانی و پیشگیری | کارگران ماهیگیری و شکار | بازرسان آتش‌سوزی جنگل و متخصصان پیشگیری | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | جنگل‌بانان | مدرسان علوم جنگل‌داری و حفاظت، آموزش عالی | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | طبیعی‌دانان پارک | ماموران گشت پلیس و کلانتر | مدیران مرتع | پلیس ترانزیت و راه‌آهن | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>کارکنان کنترل حیوانات | زیست‌شناسان | دانشمندان حفاظت | بازرسان انطباق زیست‌محیطی | برنامه‌ریزان احیای محیط‌زیست | دانشمندان و متخصصان محیط زیست، شامل بهداشت | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول آتش‌نشانی و پیشگیری | کارگران ماهیگیری و شکار | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | جنگل‌بانان | مدرسان علوم جنگلداری و حفاظت، پس از متوسطه | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | طبیعت‌شناسان پارک | ماموران گشت پلیس و کلانتر | مدیران مراتع | پلیس ترانزیت و راه‌آهن | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>مانیتورینگ | سخن گفتن | تفکر انتقادی | گوش دادن فعالانه | درک مطلب خوانده‌شده</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ایمنی و امنیت عمومی | قانون و حکومت | کامپیوتر و الکترونیک | آموزش و تربیت</t>
+          <t>زبان انگلیسی | ایمنی و امنیت عمومی | قانون و دولت | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -580,12 +580,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض همه شرایط آب و هوایی | دفعات تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا منظم بودن | در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | موقعیت‌های تعارض</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متخصصان عملیات فرودگاه | ماموران انطباق | نگهبانان عبور و مرور و پرچم‌داران | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | سرپرستان رده اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | سرپرستان رده اول کارکنان امنیتی | کارگران نگهداری بزرگراه‌ها | رانندگان کامیون سبک | متصدیان پارکینگ | همراهان مسافر | ماموران گشت پلیس و کلانتر | لوکوموتیورانان و روسای ایستگاه‌های راه‌آهن | نگهبانان امنیتی | رانندگان شاتل و شوفرها | اپراتورهای مترو و تراموا | رانندگان تاکسی | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | ماموران غربالگری امنیت حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
+          <t>متخصصان عملیات فرودگاه | افسران انطباق | نگهبانان عبور و مرور و پرچم‌داران | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول کارکنان امنیتی | کارگران نگهداری بزرگراه‌ها | رانندگان کامیون‌های سبک | متصدیان پارکینگ | متصدیان مسافران | ماموران گشت پلیس و کلانتر | رئیس قطارها و مدیران محوطه راه‌آهن | نگهبانان امنیتی | رانندگان شاتل و شوفرها | رانندگان مترو و تراموا | رانندگان تاکسی | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | غربالگران امنیتی حمل و نقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار ترسیم چهره به کمک کامپیوتر | نرم‌افزار دیسپچ به کمک کامپیوتر | Corel WordPerfect Office Suite | نرم‌افزار نقشه‌برداری جرم | نرم‌افزار پایگاه داده | DesignWare 3D EyeWitness | ESRI ArcView | نرم‌افزار ایمیل | IBM Lotus 1-2-3 | سیستم یکپارچه خودکار شناسایی اثر انگشت IAFIS | پایگاه‌های داده اطلاعات اجرای قانون | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Windows | Microsoft Word | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | شبکه ملی یکپارچه اطلاعات بالستیک NIBIN | SmartDraw Legal | SmugMug Flickr | Spillman Technologies Records Management | The CAD Zone The Crime Zone | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار طراحی چهره‌نگاری رایانه‌ای | نرم‌افزار اعزام به کمک کامپیوتر | Corel WordPerfect Office Suite | نرم‌افزار نقشه‌برداری جرم | نرم‌افزار پایگاه داده | DesignWare 3D EyeWitness | ESRI ArcView | نرم‌افزار ایمیل | IBM Lotus 1-2-3 | سیستم یکپارچه خودکار شناسایی اثر انگشت IAFIS | پایگاه‌های داده اطلاعات اجرای قانون | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Windows | Microsoft Word | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | شبکه ملی یکپارچه اطلاعات بالستیک NIBIN | SmartDraw Legal | SmugMug Flickr | Spillman Technologies Records Management | The CAD Zone The Crime Zone | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعالانه | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب خوانده‌شده | مانیتورینگ | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | قانون و حکومت | زبان انگلیسی | روان‌شناسی | خدمات مشتریان و پرسنلی | آموزش و تربیت | مخابرات | مدیریت و سازماندهی | امور اداری | کامپیوتر و الکترونیک | ارتباطات و رسانه | حمل‌ونقل | جغرافیا | جامعه‌شناسی و انسان‌شناسی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | زبان انگلیسی | روان‌شناسی | خدمات مشتری و شخصی | آموزش و پرورش | مخابرات | مدیریت و اداره | اداری | رایانه و الکترونیک | ارتباطات و رسانه | حمل و نقل | جغرافیا | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | بینایی دور | تشخیص گفتار | انعطاف‌پذیری بستار | بیان کتبی | قدرت تنه | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | سرعت بستار | هماهنگی چند عضو | قدرت ایستا | قدرت انفجاری | قدرت پویا | زمان عکس‌العمل | جهت‌گیری پاسخ | سرعت ادراکی | ثبات بازو-دست | اشتراک زمانی | حفظ کردن | اصالت | روان بودن ایده‌ها</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | بینایی دور | تشخیص گفتار | انعطاف‌پذیری بستار | بیان کتبی | قدرت تنه | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | سرعت بستار | هماهنگی چند عضو | قدرت ایستا | قدرت انفجاری | قدرت پویا | زمان عکس‌العمل | جهت‌گیری پاسخ | سرعت ادراکی | ثبات دست و بازو | تقسیم توجه | حفظ کردن | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>تعامل با مشتریان خارجی یا عموم مردم به طور کلی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت دقیق یا منظم بودن | در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | مکالمات تلفنی | دفعات تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | فضای باز، در معرض همه شرایط آب و هوایی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | در معرض شرایط نوری بسیار روشن یا ناکافی | نزدیکی فیزیکی | برخورد با افراد خشن یا متجاوز فیزیکی | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | در معرض دماهای بسیار گرم یا سرد | در معرض تجهیزات خطرناک | اهمیت تکرار وظایف مشابه | پیامد اشتباه | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
+          <t>تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | مکالمات تلفنی | فراوانی تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | فضای باز، در معرض تمام شرایط آب و هوایی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | موقعیت‌های تعارض | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | نزدیکی فیزیکی | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض تجهیزات خطرناک | اهمیت تکرار وظایف یکسان | پیامد خطا | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، دادرسان و ماموران دادرسی | ضابطان دادگستری | ماموران انطباق | پزشکان قانونی | افسران اصلاح و تربیت و زندانبانان | کارمندان دادگاه، شهرداری و مجوزها | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | سرپرستان رده اول افسران اصلاح و تربیت | سرپرستان رده اول کارگران آتش‌نشانی و پیشگیری | سرپرستان رده اول پلیس و کارآگاهان | سرپرستان رده اول کارکنان امنیتی | تحلیل‌گران اطلاعاتی | قضات، دادیاران و بازپرسان | افسران شناسایی و بایگانی پلیس | کارآگاهان و بازرسان خصوصی | افسران تعلیق مراقبتی و متخصصان درمان اصلاحی | اپراتورهای مخابراتی امنیت عمومی | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | ضابطان دادگستری | افسران انطباق | بازرسان مرگ | افسران اصلاح و تربیت و زندانبانان | کارمندان دادگاه، شهرداری و مجوز | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | تحلیلگران اطلاعاتی | قضات، قضات دادگاه‌های بدوی و قضات صلح | افسران شناسایی و سوابق پلیس | کارآگاهان و بازرسان خصوصی | افسران مشروط و متخصصان درمان اصلاحی | اپراتورهای مخابراتی امنیت عمومی | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعالانه | درک مطلب خوانده‌شده | مانیتورینگ | نگارش | یادگیری فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>قانون و حکومت | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتریان و پرسنلی | روان‌شناسی | امور اداری | کامپیوتر و الکترونیک | جغرافیا | جامعه‌شناسی و انسان‌شناسی | آموزش و تربیت | زبان خارجی</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | اداری | رایانه و الکترونیک | جغرافیا | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | زبان خارجی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه انتخابی | بینایی دور | اشتراک زمانی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه انتخابی | بینایی دور | تقسیم توجه</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | داخل ساختمان، محیط کنترل‌شده از نظر دما | مکالمات تلفنی | دفعات تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | پیامد اشتباه | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | اهمیت تکرار وظایف مشابه | در معرض آلاینده‌ها | فضای باز، در معرض همه شرایط آب و هوایی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | موقعیت‌های تعارض | در معرض شرایط نوری بسیار روشن یا ناکافی | در معرض دماهای بسیار گرم یا سرد | نامه‌ها و یادداشت‌های کتبی | in معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | سطح رقابت | سلامت و ایمنی سایر کارکنان | در معرض بیماری یا عفونت‌ها</t>
+          <t>ایمیل | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامد خطا | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض آلاینده‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | موقعیت‌های تعارض | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | نامه‌ها و یادداشت‌های کتبی | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | سطح رقابت | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | نمایندگان بار و محموله | مدیران انطباق | ماموران انطباق | کارگزاران گمرک | کارآگاهان و بازرسان جنایی | بازرسان انطباق محیطی | سرپرستان رده اول پلیس و کارآگاهان | ارزیابان، بازرسان و تحلیل‌گران تقلب | متصدیان حمل‌ونقل کالا | بازرسان و کارآگاهان اموال دولتی | تحلیل‌گران اطلاعاتی | افسران شناسایی و بایگانی پلیس | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | نگهبانان امنیتی | ارزیابان و وصول‌کنندگان مالیات، و ماموران دارایی | پلیس ترانزیت و راه‌آهن | بازرسان حمل‌ونقل | ماموران غربالگری امنیت حمل‌ونقل</t>
+          <t>بازرسان کشاورزی | نمایندگان بار و محموله | مدیران انطباق | افسران انطباق | کارگزاران گمرک | کارآگاهان و بازرسان جنایی | بازرسان انطباق زیست‌محیطی | سرپرستان خط اول پلیس و کارآگاهان | بازرسان، محققان و تحلیلگران کلاهبرداری | متصدیان حمل و نقل | بازرسان و محققان اموال دولتی | تحلیلگران اطلاعاتی | افسران شناسایی و سوابق پلیس | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | نگهبانان امنیتی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | پلیس ترانزیت و راه‌آهن | بازرسان حمل‌ونقل | غربالگران امنیتی حمل و نقل</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعالانه | تفکر انتقادی | مانیتورینگ | یادگیری فعال | نگارش | درک مطلب خوانده‌شده</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | قانون و حکومت | زبان انگلیسی | خدمات مشتریان و پرسنلی | حمل‌ونقل | آموزش و تربیت | جغرافیا | روان‌شناسی | کامپیوتر و الکترونیک | مدیریت و سازماندهی | مخابرات | ارتباطات و رسانه</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | حمل و نقل | آموزش و پرورش | جغرافیا | روان‌شناسی | رایانه و الکترونیک | مدیریت و اداره | مخابرات | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال استقرایی | وضوح گفتار | بیان کتبی | استدلال قیاسی | بینایی نزدیک | بینایی دور | تشخیص گفتار | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | درک کتبی | توجه انتخابی | توجه شنیداری | قدرت تنه | سرعت بستار | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | اصالت | روان بودن ایده‌ها | استقامت بدنی | قدرت انفجاری | قدرت ایستا | جهت‌گیری پاسخ | هماهنگی چند عضو | زبردستی دستی | ثبات بازو-دست | اشتراک زمانی | حساسیت شنوایی</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال استقرایی | وضوح گفتار | بیان کتبی | استدلال قیاسی | بینایی نزدیک | بینایی دور | تشخیص گفتار | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | درک کتبی | توجه انتخابی | توجه شنیداری | قدرت تنه | سرعت بستار | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | استقامت | قدرت انفجاری | قدرت ایستا | جهت‌گیری پاسخ | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | تقسیم توجه | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | فضای باز، در معرض همه شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | مکالمات تلفنی | دفعات تصمیم‌گیری | آزادی در تصمیم‌گیری | اهمیت دقیق یا منظم بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | موقعیت‌های تعارض | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | داخل ساختمان، محیط غیرکنترل‌شده از نظر دما | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض آلاینده‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | در معرض شرایط خطرناک | پیامد اشتباه | برخورد با افراد خشن یا متجاوز فیزیکی | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | پیامدهای کاری و نتایج سایر کارکنان</t>
+          <t>ایمیل | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | مکالمات تلفنی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | موقعیت‌های تعارض | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | محیط داخلی، بدون کنترل شرایط محیطی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | قرار گرفتن در معرض شرایط خطرناک | پیامد خطا | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان عملیات فرودگاه | ماموران انطباق | افسران اصلاح و تربیت و زندانبانان | نگهبانان عبور و مرور و پرچم‌داران | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | دیسپچرها، به جز پلیس, آتش‌نشانی و آمبولانس | بازرسان و کارآگاهان آتش‌نشانی | سرپرستان رده اول کارگران آتش‌نشانی و پیشگیری | سرپرستان رده اول پلیس و کارآگاهان | سرپرستان رده اول کارکنان امنیتی | لوکوموتیورانان | ماموران اجرای مقررات پارک | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | اپراتورهای مخابراتی امنیت عمومی | لوکوموتیورانان و روسای ایستگاه‌های راه‌آهن | نگهبانان امنیتی | اپراتورهای مترو و تراموا | ماموران غربالگری امنیت حمل‌ونقل</t>
+          <t>متخصصان عملیات فرودگاه | افسران انطباق | افسران اصلاح و تربیت و زندانبانان | نگهبانان عبور و مرور و پرچم‌داران | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | بازرسان و محققان آتش‌نشانی | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | مهندسان لوکوموتیو | ماموران اجرای مقررات پارک | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | اپراتورهای مخابراتی امنیت عمومی | رئیس قطارها و مدیران محوطه راه‌آهن | نگهبانان امنیتی | رانندگان مترو و تراموا | غربالگران امنیتی حمل و نقل</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ARK Software Ark Shelter Software | Animal Shelter Manager | CISCO Software ACS Animal Control System | Esri ArcGIS | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | Multiple Options Animal Shelter Management System | RescueConnection Software ShelterConntection | RoseRush Services Shelter Pro | نرم‌افزار SAP | TRAX Animal Control and Dog Warden Officer Software | نرم‌افزار مرورگر وب</t>
+          <t>ARK Software Ark Shelter Software | Animal Shelter Manager | CISCO Software ACS Animal Control System | Esri ArcGIS | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | Multiple Options Animal Shelter Management System | RescueConnection Software ShelterConntection | RoseRush Services Shelter Pro | نرم‌افزار SAP | TRAX Animal Control and Dog Warden Officer Software | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعالانه | سخن گفتن | تفکر انتقادی | مانیتورینگ | نگارش | درک مطلب خوانده‌شده</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | قانون و حکومت | زبان انگلیسی | خدمات مشتریان و پرسنلی | امور اداری | آموزش و تربیت | زیست‌شناسی | مخابرات | ارتباطات و رسانه | حمل‌ونقل | کامپیوتر و الکترونیک</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | اداری | آموزش و پرورش | زیست‌شناسی | مخابرات | ارتباطات و رسانه | حمل و نقل | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | درک کتبی | تشخیص گفتار | بینایی دور | بینایی نزدیک | قدرت ایستا | هماهنگی چند عضو | زبردستی دستی | ثبات بازو-دست | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | درک کتبی | تشخیص گفتار | بینایی دور | بینایی نزدیک | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | در خودروی سرپوشیده یا کار با تجهیزات سرپوشیده | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | فضای باز، در معرض همه شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | ارتباط با دیگران | دفعات تصمیم‌گیری | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش, محافظ گوش، کلاه ایمنی یا جلیقه نجات | در معرض بیماری یا عفونت‌ها | نامه‌ها و یادداشت‌های کتبی | موقعیت‌های تعارض | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌زدگی‌ها | داخل ساختمان، محیط غیرکنترل‌شده از نظر دما | اهمیت دقیق یا منظم بودن | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض دماهای بسیار گرم یا سرد | پیامد اشتباه | داخل ساختمان، محیط کنترل‌شده از نظر دما | فشار زمانی | در معرض شرایط نوری بسیار روشن یا ناکافی | نزدیکی فیزیکی | فضای باز، زیر سرپناه | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | اهمیت تکرار وظایف مشابه | در معرض فضای کاری تنگ، موقعیت‌های نامناسب بدنی</t>
+          <t>مکالمات تلفنی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | فضای باز، در معرض تمام شرایط آب و هوایی | تعامل با مشتریان خارجی یا عموم مردم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | ارتباط با دیگران | فراوانی تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نامه‌ها و یادداشت‌های کتبی | موقعیت‌های تعارض | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | محیط داخلی، بدون کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامد خطا | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | نزدیکی فیزیکی | فضای باز، زیر سقف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | پرورش‌دهندگان حیوانات | مراقبان حیوانات | دانشمندان علوم دامی | مربیان حیوانات | پزشکان قانونی | افسران اصلاح و تربیت و زندانبانان | کارآگاهان و بازرسان جنایی | بازرسان انطباق محیطی | کارگران مزارع، حیوانات مزرعه، دامداری و آبزی‌پروری | محیط‌بانان و جنگل‌بانان | افسران شناسایی و بایگانی پلیس | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن | دامپزشکان | دستیاران دامپزشک و مراقبان حیوانات آزمایشگاهی | تکنسین‌ها و کاردان‌های دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>بازرسان کشاورزی | پرورش‌دهندگان حیوانات | مراقبان حیوانات | دانشمندان علوم دامی | مربیان حیوانات | بازرسان مرگ | افسران اصلاح و تربیت و زندانبانان | کارآگاهان و بازرسان جنایی | بازرسان انطباق زیست‌محیطی | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | محیط‌بانان و جنگل‌بانان | افسران شناسایی و سوابق پلیس | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن | دامپزشکان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعالانه | سخن گفتن | درک مطلب خوانده‌شده | تفکر انتقادی | نگارش | یادگیری فعال | مانیتورینگ</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و پرسنلی | قانون و حکومت | کامپیوتر و الکترونیک | امور اداری | مدیریت و سازماندهی | ایمنی و امنیت عمومی | روان‌شناسی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | رایانه و الکترونیک | اداری | مدیریت و اداره | ایمنی و امنیت عمومی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | درک کتبی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری بستار | بینایی دور | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | سرعت ادراکی | اصالت</t>
+          <t>استدلال استقرایی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | درک کتبی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری بستار | بینایی دور | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | سرعت ادراکی | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | اهمیت دقیق یا منظم بودن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | فشار زمانی | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | دفعات تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | داخل ساختمان، محیط کنترل‌شده از نظر دما</t>
+          <t>مکالمات تلفنی | ایمیل | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | فشار زمانی | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ارزیابان، بررسی‌کنندگان و بازرسان خسارت بیمه | ماموران انطباق | پزشکان قانونی | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | کارآگاهان و بازرسان جنایی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان مالی | سرپرستان رده اول پلیس و کارآگاهان | سرپرستان رده اول کارکنان امنیتی | تکنسین‌های علوم جنایی | ارزیابان، بازرسان و تحلیل‌گران تقلب | بازرسان و کارآگاهان اموال دولتی | تحلیل‌گران اطلاعاتی | وکلا | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | دستیاران حقوقی و پاراکارها | افسران شناسایی و بایگانی پلیس | ماموران گشت پلیس و کلانتر | متخصصان پیشگیری از خسارت خرده‌فروشی</t>
+          <t>تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | افسران انطباق | بازرسان مرگ | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | کارآگاهان و بازرسان جنایی | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان مالی | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | تکنسین‌های علوم قانونی | بازرسان، محققان و تحلیلگران کلاهبرداری | بازرسان و محققان اموال دولتی | تحلیلگران اطلاعاتی | وکلا | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | پارالیگال‌ها و دستیاران حقوقی | افسران شناسایی و سوابق پلیس | ماموران گشت پلیس و کلانتر | متخصصان پیشگیری از خسارت خرده‌فروشی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | سخن گفتن | گوش دادن فعالانه | درک مطلب خوانده‌شده | نگارش | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | ریاضیات | امور اداری | آموزش و تربیت | خدمات مشتریان و پرسنلی | مدیریت و سازماندهی</t>
+          <t>زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | ریاضیات | اداری | آموزش و پرورش | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | توجه انتخابی | بینایی دور | درک شفاهی | بینایی نزدیک | بیان کتبی | استدلال استقرایی | بیان شفاهی | انعطاف‌پذیری بستار | استدلال قیاسی | سرعت ادراکی | تشخیص گفتار | وضوح گفتار | سرعت بستار | ترتیب‌دهی اطلاعات | درک کتبی | اشتراک زمانی</t>
+          <t>حساسیت به مسئله | توجه انتخابی | بینایی دور | درک شفاهی | بینایی نزدیک | بیان کتبی | استدلال استقرایی | بیان شفاهی | انعطاف‌پذیری بستار | استدلال قیاسی | سرعت ادراکی | تشخیص گفتار | وضوح گفتار | سرعت بستار | ترتیب‌دهی اطلاعات | درک کتبی | تقسیم توجه</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده از نظر دما | مکالمات تلفنی | اهمیت دقیق یا منظم بودن | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف مشابه | کار با یا مشارکت در یک گروه کاری یا تیم | دفعات تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | موقعیت‌های تعارض | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | پیامد اشتباه</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | موقعیت‌های تعارض | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | پیامد خطا</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اپراتورهای دوربین، تلویزیون، ویدیو و فیلم | مدیران انطباق | متخصصان پشتیبانی شبکه کامپیوتری | بازرسان ساخت‌وساز و ساختمان | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌شناسی دیجیتال | سرپرستان رده اول کارکنان خدمات قمار | سرپرستان رده اول کارکنان امنیتی | ارزیابان، بازرسان و تحلیل‌گران تقلب | مدیران قمار | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران اطلاعاتی | تحلیل‌گران مدیریت | تست‌کنندگان نفوذ | کارآگاهان و بازرسان خصوصی | متخصصان پیشگیری از خسارت خرده‌فروشی | متخصصان مدیریت امنیت | مدیران امنیت | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط</t>
+          <t>اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | مدیران انطباق | متخصصان پشتیبانی شبکه کامپیوتری | بازرسان ساختمان و ساخت‌وساز | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌شناسی دیجیتال | سرپرستان خط اول کارگران خدمات قمار | سرپرستان خط اول کارکنان امنیتی | بازرسان، محققان و تحلیلگران کلاهبرداری | مدیران قماربازی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیلگران اطلاعاتی | تحلیل‌گران مدیریت | کارشناسان آزمون نفوذ | کارآگاهان و بازرسان خصوصی | متخصصان پیشگیری از خسارت خرده‌فروشی | متخصصان مدیریت امنیت | مدیران امنیتی | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعالانه | مانیتورینگ | سخن گفتن | تفکر انتقادی | درک مطلب خوانده‌شده</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و پرسنلی | زبان انگلیسی | کامپیوتر و الکترونیک | مدیریت و سازماندهی | آموزش و تربیت | مخابرات | امور اداری | قانون و حکومت | درمان و مشاوره | روان‌شناسی | پزشکی و دندانپزشکی</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | مدیریت و اداره | آموزش و پرورش | مخابرات | اداری | قانون و دولت | درمان و مشاوره | روان‌شناسی | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>سلامت و ایمنی سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | ارتباط با دیگران | مکالمات تلفنی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف مشابه | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا منظم بودن | تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان، محیط کنترل‌شده از نظر دما | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | موقعیت‌های تعارض | دفعات تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>سلامت و ایمنی سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | مکالمات تلفنی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | موقعیت‌های تعارض | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متخصصان عملیات فرودگاه | رانندگان و همراهان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | افسران اصلاح و تربیت و زندانبانان | نگهبانان عبور و مرور و پرچم‌داران | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | بازرسان و کارآگاهان آتش‌نشانی | آتش‌نشانان | سرپرستان رده اول کارگران آتش‌نشانی و پیشگیری | سرپرستان رده اول کارکنان امنیتی | بازرسان آتش‌سوزی جنگل و متخصصان پیشگیری | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | ماموران اجرای مقررات پارک | ماموران گشت پلیس و کلانتر | اپراتورهای مخابراتی امنیت عمومی | متخصصان پیشگیری از خسارت خرده‌فروشی | متخصصان مدیریت امنیت | مدیران امنیت | پلیس ترانزیت و راه‌آهن | ماموران غربالگری امنیت حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
+          <t>متخصصان عملیات فرودگاه | رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | افسران اصلاح و تربیت و زندانبانان | نگهبانان عبور و مرور و پرچم‌داران | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | بازرسان و محققان آتش‌نشانی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول کارکنان امنیتی | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | ماموران اجرای مقررات پارک | ماموران گشت پلیس و کلانتر | اپراتورهای مخابراتی امنیت عمومی | متخصصان پیشگیری از خسارت خرده‌فروشی | متخصصان مدیریت امنیت | مدیران امنیتی | پلیس ترانزیت و راه‌آهن | غربالگران امنیتی حمل و نقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و پرسنلی | زبان انگلیسی</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض همه شرایط آب و هوایی | صرف زمان برای ایستادن | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | در معرض دماهای بسیار گرم یا سرد | در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | دفعات تصمیم‌گیری | نزدیکی فیزیکی | ارتباط با دیگران | صرف زمان برای پیاده‌روی یا دویدن | پیامد اشتباه | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا منظم بودن | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | ارتباط با دیگران | صرف زمان برای راه رفتن یا دویدن | پیامد خطا | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کنترل‌کنندگان ترافیک هوایی | متصدیان پل و قفل کانال | رانندگان اتوبوس، ترانزیت و بین‌شهری | دیسپچرها، به جز پلیس، آتش‌نشانی و آمبولانس | کارگران نگهداری بزرگراه‌ها | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | لوکوموتیورانان | ماموران اجرای مقررات پارک | همراهان مسافر | ماموران گشت پلیس و کلانتر | اپراتورهای مخابراتی امنیت عمومی | مهندسان محوطه راه‌آهن، اپراتورهای دینکی و هاستلرها | اپراتورهای ترمز، سیگنال و سوزن‌بان راه‌آهن و آتش‌نشانان لوکوموتیو | لوکوموتیورانان و روسای ایستگاه‌های راه‌آهن | ناظران اتوبوس مدرسه | نگهبانان امنیتی | اپراتورهای مترو و تراموا | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | ماموران غربالگری امنیت حمل‌ونقل</t>
+          <t>کنترلرهای ترافیک هوایی | متصدیان پل و کانال | رانندگان اتوبوس، ترانزیت و بین‌شهری | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | کارگران نگهداری بزرگراه‌ها | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | مهندسان لوکوموتیو | ماموران اجرای مقررات پارک | متصدیان مسافران | ماموران گشت پلیس و کلانتر | اپراتورهای مخابراتی امنیت عمومی | مهندسان محوطه راه‌آهن، اپراتورهای لکوموتیو مانوری و متصدیان آماده‌سازی لکوموتیو | اپراتورهای ترمز، علائم و سوزن راه‌آهن و آتش‌کاران لکوموتیو | رئیس قطارها و مدیران محوطه راه‌آهن | مراقبین اتوبوس مدرسه | نگهبانان امنیتی | رانندگان مترو و تراموا | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | غربالگران امنیتی حمل و نقل</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0055_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0055_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | ایمنی و امنیت عمومی | زیست‌شناسی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی | جغرافیا | جامعه‌شناسی و مردم‌شناسی | آموزش و تدریس | مدیریت و امور اداری | امور اداری و دفتری | رایانه و الکترونیک | ارتباطات و رسانه</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | زیست‌شناسی | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | جغرافیا | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | مدیریت و اداره | اداری | رایانه و الکترونیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال استقرایی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | دید نزدیک | دید دور | درک کتبی | بیان کتبی | انعطاف‌پذیری در جمع‌بندی ذهنی | جهت‌یابی فضایی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | سرعت جمع‌بندی ذهنی | درک عمق | استقامت جسمانی | هماهنگی اندام‌ها | دقت کنترل حرکتی | تقسیم توجه | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال استقرایی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | بینایی دور | درک کتبی | بیان کتبی | انعطاف‌پذیری بستار | جهت‌گیری فضایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | سرعت بستار | درک عمق | استقامت | هماهنگی چند عضو | دقت کنترل | تقسیم توجه | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ماموران کنترل حیوانات | زیست‌شناسان | دانشمندان حفاظت محیط زیست | بازرسان انطباق زیست‌محیطی | برنامه‌ریزان بازسازی زیست‌محیطی | دانشمندان و کارشناسان محیط زیست و بهداشت محیط | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول آتش‌نشانان و ماموران پیشگیری از آتش‌سوزی | کارگران صید و شکار | کارشناسان بازرسی و پیشگیری از آتش‌سوزی جنگل‌ها | تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت محیط زیست | کارشناسان جنگل‌داری | مدرسان علوم جنگل‌داری و حفاظت محیط زیست در آموزش عالی | نجات‌غریق‌ها، گشت اسکی و سایر ماموران خدمات حفاظتی تفریحی | کارشناسان طبیعت و پارک‌های ملی | ماموران گشت پلیس و کلانتری | مدیران مراتع | پلیس ترانزیت و راه‌آهن | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>ماموران کنترل و ساماندهی حیوانات | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | بازرسان رعایت ضوابط زیست‌محیطی | برنامه‌ریزان احیای محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | صیادان، ماهیگیران و شکارچیان | بازرسان و کارشناسان پیشگیری از حریق جنگل | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | استادان و مدرسان جنگلداری و منابع طبیعی در دانشگاه‌ها و مراکز آموزش عالی | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | طبیعت‌شناسان و کارشناسان پارک‌های ملی | ماموران گشت پلیس و کلانتری | مدیران و کارشناسان مدیریت مراتع | پلیس ترانزیت و راه‌آهن | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ایمنی و امنیت عمومی | حقوق و مقررات دولتی | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>زبان انگلیسی | ایمنی و امنیت عمومی | قانون و دولت | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | مرتب‌سازی اطلاعات | درک شفاهی | دید نزدیک | تشخیص گفتار | دید دور | حساسیت به مسئله | بیان کتبی | سرعت ادراک | توجه انتخابی | استدلال استقرایی | استدلال قیاسی | درک کتبی | دقت کنترل حرکتی</t>
+          <t>بیان شفاهی | وضوح گفتار | ترتیب‌دهی اطلاعات | درک شفاهی | بینایی نزدیک | تشخیص گفتار | بینایی دور | حساسیت به مسئله | بیان کتبی | سرعت ادراکی | توجه انتخابی | استدلال استقرایی | استدلال قیاسی | درک کتبی | دقت کنترل</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متخصصان عملیات فرودگاهی | کارشناسان انطباق با قوانین و مقررات | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | متصدیان اعزام و مخابرات به غیر از پلیس، آتش‌نشانی و اورژانس | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی مواد | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارگران نگهداری و راهداری بزرگراه‌ها | رانندگان وانت و کامیونت سبک | پارکبانان | متصدیان خدمات مسافران | ماموران گشت پلیس و کلانتری | متصدیان قطار و روسای ایستگاه راه‌آهن | نگهبانان و ماموران حراست | رانندگان سرویس و تشریفات | راهبران مترو و قطار شهری | رانندگان تاکسی | تکنسین‌های ترافیک و عبور و مرور | پلیس ترانزیت و راه‌آهن | ماموران بازرسی و غربالگری امنیت حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سامانه‌های حمل‌ونقل غیرهوایی</t>
+          <t>کارشناسان عملیات فرودگاهی | کارشناسان پایش انطباق و بازرسی مقرراتی | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارگران راهداری و نگهداری جاده‌ها | رانندگان خودروهای باربری سبک و وانت‌بارها | متصدیان پارکینگ | مهمانداران و متصدیان خدمات مسافران | ماموران گشت پلیس و کلانتری | رؤسای قطار و مدیران محوطه راه‌آهن | نگهبانان و ماموران حراست | رانندگان خودروهای سرویس و تشریفات | رانندگان مترو و تراموا | رانندگان تاکسی | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | درک مطلب | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | زبان انگلیسی | روان‌شناسی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | مخابرات | مدیریت و امور اداری | امور اداری و دفتری | رایانه و الکترونیک | ارتباطات و رسانه | ترابری و حمل‌ونقل | جغرافیا | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | زبان انگلیسی | روان‌شناسی | خدمات مشتری و شخصی | آموزش و پرورش | مخابرات | مدیریت و اداره | اداری | رایانه و الکترونیک | ارتباطات و رسانه | حمل و نقل | جغرافیا | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | وضوح گفتار | مرتب‌سازی اطلاعات | دید نزدیک | دید دور | تشخیص گفتار | انعطاف‌پذیری در جمع‌بندی ذهنی | بیان کتبی | قدرت عضلات تنه | انعطاف‌پذیری در دسته‌بندی | توجه انتخابی | سرعت جمع‌بندی ذهنی | هماهنگی اندام‌ها | قدرت ایستا | توان انفجاری | قدرت پویا | سرعت واکنش | جهت‌گیری به محرک | سرعت ادراک | پایداری دست و بازو | تقسیم توجه | به‌خاطرسپاری | خلاقیت و ابتکار | روانی ایده‌ها</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | بینایی دور | تشخیص گفتار | انعطاف‌پذیری بستار | بیان کتبی | قدرت تنه | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | سرعت بستار | هماهنگی چند عضو | قدرت ایستا | قدرت انفجاری | قدرت پویا | زمان عکس‌العمل | جهت‌گیری پاسخ | سرعت ادراکی | ثبات دست و بازو | تقسیم توجه | حفظ کردن | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، دادرسان و مسئولان استماع | ضابطان اجرای احکام و تشریفات دادگاه | کارشناسان انطباق با قوانین و مقررات | کارشناسان پزشکی قانونی و معاینه اجساد | ماموران زندان و ندامتگاه | کارمندان دادگاه، شهرداری و امور صدور پروانه | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان کشف جرم | سرپرستان رده‌اول ماموران زندان | سرپرستان رده‌اول آتش‌نشانان و ماموران پیشگیری از آتش‌سوزی | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | تحلیل‌گران اطلاعاتی و امنیتی | قضات، دادیاران و دادرسان | کارشناسان تشخیص هویت و سوابق کیفری پلیس | کارآگاهان و بازرسان خصوصی | مددکاران پیگیری و اصلاح و تربیت و مراقبت پس از خروج | متصدیان مخابرات ایمنی و فوریت‌های پلیسی | نگهبانان و ماموران حراست | پلیس ترانزیت و راه‌آهن</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | مأموران انتظامات و حفاظت دادگاه | کارشناسان پایش انطباق و بازرسی مقرراتی | پزشکان قانونی و بازرسان مرگ مشکوک | مأموران زندان و بازداشتگاه | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | قضات دادگاه و دادیاران | کارشناسان تشخیص هویت و ثبت سوابق پلیس | کارآگاهان و بازرسان خصوصی | مددکاران قضایی و متخصصان اصلاح و تربیت | اپراتورهای فوریت‌های پلیسی و امدادی | نگهبانان و ماموران حراست | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی | امور اداری و دفتری | رایانه و الکترونیک | جغرافیا | جامعه‌شناسی و مردم‌شناسی | آموزش و تدریس | زبان خارجی</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | اداری | رایانه و الکترونیک | جغرافیا | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | زبان خارجی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | دید نزدیک | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری در جمع‌بندی ذهنی | مرتب‌سازی اطلاعات | سرعت ادراک | توجه انتخابی | دید دور | تقسیم توجه</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه انتخابی | بینایی دور | تقسیم توجه</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بازرسان محصولات کشاورزی | متصدیان ترخیص و خدمات بار هوایی و دریایی | مدیران انطباق با مقررات | کارشناسان انطباق با قوانین و مقررات | کارگزاران گمرکی و ترخیص‌کاران | کارآگاهان و بازرسان کشف جرم | بازرسان انطباق زیست‌محیطی | سرپرستان رده‌اول پلیس و کارآگاهان | کارشناسان و تحلیل‌گران بررسی تخلفات مالی | متصدیان حمل‌ونقل و فورواردرها | بازرسان و حسابرسان اموال و دارایی‌های دولتی | تحلیل‌گران اطلاعاتی و امنیتی | کارشناسان تشخیص هویت و سوابق کیفری پلیس | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | نگهبانان و ماموران حراست | ممیزان و ماموران وصول مالیات | پلیس ترانزیت و راه‌آهن | بازرسان حمل‌ونقل | ماموران بازرسی و غربالگری امنیت حمل‌ونقل</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | کارگزاران حمل‌ونقل و بار | مدیران تطبیق و نظارت مقرراتی | کارشناسان پایش انطباق و بازرسی مقرراتی | حق‌العمل‌کاران و کارگزاران گمرکی | کارآگاهان و بازرسان جنایی | بازرسان رعایت ضوابط زیست‌محیطی | سرپرستان رده‌اول پلیس و کارآگاهان | کارشناسان بازرسی، کشف و تحلیل تقلب | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | بازرسان و ممیزان اموال دولتی | تحلیل‌گران داده‌ها و اطلاعات امنیتی | کارشناسان تشخیص هویت و ثبت سوابق پلیس | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | نگهبانان و ماموران حراست | ممیزان، ماموران وصول و کارشناسان مالیاتی | پلیس ترانزیت و راه‌آهن | بازرسان ترابری و حمل‌ونقل | ماموران بازرسی و کنترل امنیتی حمل‌ونقل</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ترابری و حمل‌ونقل | آموزش و تدریس | جغرافیا | روان‌شناسی | رایانه و الکترونیک | مدیریت و امور اداری | مخابرات | ارتباطات و رسانه</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | حمل و نقل | آموزش و پرورش | جغرافیا | روان‌شناسی | رایانه و الکترونیک | مدیریت و اداره | مخابرات | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال استقرایی | وضوح گفتار | بیان کتبی | استدلال قیاسی | دید نزدیک | دید دور | تشخیص گفتار | انعطاف‌پذیری در جمع‌بندی ذهنی | مرتب‌سازی اطلاعات | درک کتبی | توجه انتخابی | توجه شنیداری | قدرت عضلات تنه | سرعت جمع‌بندی ذهنی | سرعت ادراک | انعطاف‌پذیری در دسته‌بندی | خلاقیت و ابتکار | روانی ایده‌ها | استقامت جسمانی | توان انفجاری | قدرت ایستا | جهت‌گیری به محرک | هماهنگی اندام‌ها | چابکی دستی | پایداری دست و بازو | تقسیم توجه | حساسیت شنیداری</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال استقرایی | وضوح گفتار | بیان کتبی | استدلال قیاسی | بینایی نزدیک | بینایی دور | تشخیص گفتار | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | درک کتبی | توجه انتخابی | توجه شنیداری | قدرت تنه | سرعت بستار | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | استقامت | قدرت انفجاری | قدرت ایستا | جهت‌گیری پاسخ | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | تقسیم توجه | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متخصصان عملیات فرودگاهی | کارشناسان انطباق با قوانین و مقررات | ماموران زندان و ندامتگاه | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان کشف جرم | متصدیان اعزام و مخابرات به غیر از پلیس، آتش‌نشانی و اورژانس | کارشناسان و بازرسان آتش‌نشانی | سرپرستان رده‌اول آتش‌نشانان و ماموران پیشگیری از آتش‌سوزی | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | لکوموتیورانان | ماموران کنترل و اعمال قانون پارک دوبله و توقف | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | متصدیان مخابرات ایمنی و فوریت‌های پلیسی | متصدیان قطار و روسای ایستگاه راه‌آهن | نگهبانان و ماموران حراست | راهبران مترو و قطار شهری | ماموران بازرسی و غربالگری امنیت حمل‌ونقل</t>
+          <t>کارشناسان عملیات فرودگاهی | کارشناسان پایش انطباق و بازرسی مقرراتی | مأموران زندان و بازداشتگاه | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | متصدیان دیسپاچ و اعزام | بازرسان و کارشناسان بررسی علل حریق | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | لکوموتیورانان | ماموران کنترل و اعمال قانون پارک دوبله و توقف | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | اپراتورهای فوریت‌های پلیسی و امدادی | رؤسای قطار و مدیران محوطه راه‌آهن | نگهبانان و ماموران حراست | رانندگان مترو و تراموا | ماموران بازرسی و کنترل امنیتی حمل‌ونقل</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | نگارش | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | امور اداری و دفتری | آموزش و تدریس | زیست‌شناسی | مخابرات | ارتباطات و رسانه | ترابری و حمل‌ونقل | رایانه و الکترونیک</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | اداری | آموزش و پرورش | زیست‌شناسی | مخابرات | ارتباطات و رسانه | حمل و نقل | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | درک کتبی | تشخیص گفتار | دید دور | دید نزدیک | قدرت ایستا | هماهنگی اندام‌ها | چابکی دستی | پایداری دست و بازو | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | بیان کتبی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | وضوح گفتار | استدلال استقرایی | درک کتبی | تشخیص گفتار | بینایی دور | بینایی نزدیک | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>بازرسان محصولات کشاورزی | پرورش‌دهندگان دام و حیوانات | متصدیان مراقبت و نگهداری حیوانات | دانشمندان علوم دامی | مربیان آموزش حیوانات | کارشناسان پزشکی قانونی و معاینه اجساد | ماموران زندان و ندامتگاه | کارآگاهان و بازرسان کشف جرم | بازرسان انطباق زیست‌محیطی | کارگران دامپروری، پرورش آبزیان و امور دام | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | کارشناسان تشخیص هویت و سوابق کیفری پلیس | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | نگهبانان و ماموران حراست | پلیس ترانزیت و راه‌آهن | دامپزشکان | دستیاران دامپزشکی و متصدیان حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | تکنسین‌ها و کارشناسان اصلاح نژاد و پرورش دام | مراقبان و نگهداران حیوانات | متخصصان علوم دامی | مربیان و رام‌کنندگان حیوانات | پزشکان قانونی و بازرسان مرگ مشکوک | مأموران زندان و بازداشتگاه | کارآگاهان و بازرسان جنایی | بازرسان رعایت ضوابط زیست‌محیطی | کارگران پرورش دام، طیور و آبزیان | محیط‌بانان و ماموران حفاظت شیلات و حیات وحش | کارشناسان تشخیص هویت و ثبت سوابق پلیس | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | نگهبانان و ماموران حراست | پلیس ترانزیت و راه‌آهن | دامپزشکان | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | رایانه و الکترونیک | امور اداری و دفتری | مدیریت و امور اداری | ایمنی و امنیت عمومی | روان‌شناسی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | رایانه و الکترونیک | اداری | مدیریت و اداره | ایمنی و امنیت عمومی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | درک کتبی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری در جمع‌بندی ذهنی | دید دور | انعطاف‌پذیری در دسته‌بندی | روانی ایده‌ها | سرعت ادراک | خلاقیت و ابتکار</t>
+          <t>استدلال استقرایی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | درک کتبی | بیان کتبی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری بستار | بینایی دور | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | سرعت ادراکی | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارشناسان ارزیابی، رسیدگی و خسارت بیمه | کارشناسان انطباق با قوانین و مقررات | کارشناسان پزشکی قانونی و معاینه اجساد | متصدیان تایید، استعلام و اعتبار‌سنجی اسناد | کارآگاهان و بازرسان کشف جرم | مصاحبه‌گران تعیین صلاحیت متقاضیان برنامه‌های دولتی | ممیزان و کارشناسان مالی و مالیاتی | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | تکنسین‌های علوم آزمایشگاهی و صحنه جرم | کارشناسان و تحلیل‌گران بررسی تخلفات مالی | بازرسان و حسابرسان اموال و دارایی‌های دولتی | تحلیل‌گران اطلاعاتی و امنیتی | وکلا | مسئولان دفاتر و دستیاران امور حقوقی | تحلیل‌گران مدیریت و بهبود فرآیندها | دستیاران حقوقی و پارالیگال‌ها | کارشناسان تشخیص هویت و سوابق کیفری پلیس | ماموران گشت پلیس و کلانتری | کارشناسان حفاظت و پیشگیری از خسارت فروشگاهی</t>
+          <t>کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان پایش انطباق و بازرسی مقرراتی | پزشکان قانونی و بازرسان مرگ مشکوک | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارآگاهان و بازرسان جنایی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | بازرسان و ارزیابان مالی | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کارشناسان بازرسی، کشف و تحلیل تقلب | بازرسان و ممیزان اموال دولتی | تحلیل‌گران داده‌ها و اطلاعات امنیتی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و دستیاران امور حقوقی | کارشناسان تشخیص هویت و ثبت سوابق پلیس | ماموران گشت پلیس و کلانتری | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | ریاضیات | امور اداری و دفتری | آموزش و تدریس | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | ریاضیات | اداری | آموزش و پرورش | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | توجه انتخابی | دید دور | درک شفاهی | دید نزدیک | بیان کتبی | استدلال استقرایی | بیان شفاهی | انعطاف‌پذیری در جمع‌بندی ذهنی | استدلال قیاسی | سرعت ادراک | تشخیص گفتار | وضوح گفتار | سرعت جمع‌بندی ذهنی | مرتب‌سازی اطلاعات | درک کتبی | تقسیم توجه</t>
+          <t>حساسیت به مسئله | توجه انتخابی | بینایی دور | درک شفاهی | بینایی نزدیک | بیان کتبی | استدلال استقرایی | بیان شفاهی | انعطاف‌پذیری بستار | استدلال قیاسی | سرعت ادراکی | تشخیص گفتار | وضوح گفتار | سرعت بستار | ترتیب‌دهی اطلاعات | درک کتبی | تقسیم توجه</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تصویربرداران تلویزیون، ویدئو و سینما | مدیران انطباق با مقررات | کارشناسان پشتیبانی شبکه‌های رایانه‌ای | بازرسان ساختمان و سازه | کارآگاهان و بازرسان کشف جرم | تحلیل‌گران جرایم سایبری و ادله دیجیتال | سرپرستان رده‌اول کارکنان خدمات سرگرمی و بازی | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارشناسان و تحلیل‌گران بررسی تخلفات مالی | مدیران اماکن سرگرمی و بازی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران اطلاعاتی و امنیتی | تحلیل‌گران مدیریت و بهبود فرآیندها | کارشناسان آزمون نفوذپذیری و تست نفوذ | کارآگاهان و بازرسان خصوصی | کارشناسان حفاظت و پیشگیری از خسارت فروشگاهی | متخصصان مدیریت امنیت و حراست | مدیران حراست و حفاظت فیزیکی | نصابان و تعمیرکاران تجهیزات مخابراتی غیر از خطوط شبکه</t>
+          <t>تصویربرداران تلویزیون، ویدیو و سینما | مدیران تطبیق و نظارت مقرراتی | متخصصان پشتیبانی شبکه رایانه‌ای | بازرسان ساخت‌وساز و ساختمان | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارشناسان بازرسی، کشف و تحلیل تقلب | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | کارشناسان تحلیل مدیریت و روش‌ها | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارآگاهان و بازرسان خصوصی | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | مدیریت و امور اداری | آموزش و تدریس | مخابرات | امور اداری و دفتری | حقوق و مقررات دولتی | مشاوره و راهنمایی | روان‌شناسی | پزشکی و دندان‌پزشکی</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | مدیریت و اداره | آموزش و پرورش | مخابرات | اداری | قانون و دولت | درمان و مشاوره | روان‌شناسی | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید دور | درک شفاهی | تشخیص گفتار | دید نزدیک | توجه انتخابی | بیان شفاهی | وضوح گفتار | استدلال قیاسی | انعطاف‌پذیری در جمع‌بندی ذهنی | مرتب‌سازی اطلاعات | استدلال استقرایی | درک کتبی</t>
+          <t>حساسیت به مسئله | بینایی دور | درک شفاهی | تشخیص گفتار | بینایی نزدیک | توجه انتخابی | بیان شفاهی | وضوح گفتار | استدلال قیاسی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | استدلال استقرایی | درک کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متخصصان عملیات فرودگاهی | رانندگان و خدمه آمبولانس غیر از تکنسین‌های فوریت‌های پزشکی | ماموران زندان و ندامتگاه | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | متصدیان اعزام و مخابرات به غیر از پلیس، آتش‌نشانی و اورژانس | کارشناسان و بازرسان آتش‌نشانی | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانان و ماموران پیشگیری از آتش‌سوزی | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارشناسان بازرسی و پیشگیری از آتش‌سوزی جنگل‌ها | نجات‌غریق‌ها، گشت اسکی و سایر ماموران خدمات حفاظتی تفریحی | ماموران کنترل و اعمال قانون پارک دوبله و توقف | ماموران گشت پلیس و کلانتری | متصدیان مخابرات ایمنی و فوریت‌های پلیسی | کارشناسان حفاظت و پیشگیری از خسارت فروشگاهی | متخصصان مدیریت امنیت و حراست | مدیران حراست و حفاظت فیزیکی | پلیس ترانزیت و راه‌آهن | ماموران بازرسی و غربالگری امنیت حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سامانه‌های حمل‌ونقل غیرهوایی</t>
+          <t>کارشناسان عملیات فرودگاهی | رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | مأموران زندان و بازداشتگاه | نگهبانان عبور و مرور و پرچم‌داران ترافیکی | متصدیان دیسپاچ و اعزام | بازرسان و کارشناسان بررسی علل حریق | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول کارکنان حراست و انتظامات | بازرسان و کارشناسان پیشگیری از حریق جنگل | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | ماموران کنترل و اعمال قانون پارک دوبله و توقف | ماموران گشت پلیس و کلانتری | اپراتورهای فوریت‌های پلیسی و امدادی | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | پلیس ترانزیت و راه‌آهن | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | وضوح گفتار | دید دور | توجه انتخابی | تشخیص گفتار | استدلال قیاسی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | وضوح گفتار | بینایی دور | توجه انتخابی | تشخیص گفتار | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کنترل‌کنندگان ترافیک هوایی | متصدیان پل‌های متحرک و آب‌بندها | رانندگان اتوبوس‌های شهری و بین‌شهری | متصدیان اعزام و مخابرات به غیر از پلیس، آتش‌نشانی و اورژانس | کارگران نگهداری و راهداری بزرگراه‌ها | نجات‌غریق‌ها، گشت اسکی و سایر ماموران خدمات حفاظتی تفریحی | لکوموتیورانان | ماموران کنترل و اعمال قانون پارک دوبله و توقف | متصدیان خدمات مسافران | ماموران گشت پلیس و کلانتری | متصدیان مخابرات ایمنی و فوریت‌های پلیسی | مهندسان محوطه ریلی، راهبران لکوموتیو شانتینگ و جابه‌جاکنندگان واگن | متصدیان ترمز، سوزن‌بانی، علائم راه‌آهن و کمک‌لکوموتیورانان | متصدیان قطار و روسای ایستگاه راه‌آهن | ناظران و همراهان اتوبوس مدرسه | نگهبانان و ماموران حراست | راهبران مترو و قطار شهری | تکنسین‌های ترافیک و عبور و مرور | پلیس ترانزیت و راه‌آهن | ماموران بازرسی و غربالگری امنیت حمل‌ونقل</t>
+          <t>کنترلرهای ترافیک هوایی | متصدیان پل‌های متحرک و حوضچه‌های آرامش | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | متصدیان دیسپاچ و اعزام | کارگران راهداری و نگهداری جاده‌ها | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | لکوموتیورانان | ماموران کنترل و اعمال قانون پارک دوبله و توقف | مهمانداران و متصدیان خدمات مسافران | ماموران گشت پلیس و کلانتری | اپراتورهای فوریت‌های پلیسی و امدادی | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | مراقبین و متصدیان سرویس مدارس | نگهبانان و ماموران حراست | رانندگان مترو و تراموا | تکنسین‌های ترافیک | پلیس ترانزیت و راه‌آهن | ماموران بازرسی و کنترل امنیتی حمل‌ونقل</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
